--- a/samples/ss_pedan12_ingest.xlsx
+++ b/samples/ss_pedan12_ingest.xlsx
@@ -631,31 +631,21 @@
           <t>500 kV</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr"/>
-      <c r="H2" t="inlineStr"/>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr"/>
       <c r="N2" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
         <is>
           <t>Jawa Tengah</t>
         </is>
       </c>
-      <c r="S2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -702,15 +692,11 @@
       <c r="J3" t="n">
         <v>1</v>
       </c>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Rawan</t>
@@ -726,7 +712,6 @@
           <t>Jawa Tengah</t>
         </is>
       </c>
-      <c r="S3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -773,15 +758,11 @@
       <c r="J4" t="n">
         <v>1</v>
       </c>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Rawan</t>
@@ -797,7 +778,6 @@
           <t>Jawa Tengah</t>
         </is>
       </c>
-      <c r="S4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -826,19 +806,11 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr"/>
-      <c r="H5" t="inlineStr"/>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr"/>
       <c r="N5" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Rawan</t>
@@ -854,7 +826,6 @@
           <t>Jawa Tengah</t>
         </is>
       </c>
-      <c r="S5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -883,19 +854,11 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr"/>
-      <c r="H6" t="inlineStr"/>
-      <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr"/>
       <c r="N6" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Rawan</t>
@@ -911,7 +874,6 @@
           <t>Jawa Tengah</t>
         </is>
       </c>
-      <c r="S6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -940,19 +902,11 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr"/>
-      <c r="H7" t="inlineStr"/>
-      <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr"/>
       <c r="N7" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Rawan</t>
@@ -968,7 +922,6 @@
           <t>Jawa Tengah</t>
         </is>
       </c>
-      <c r="S7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -997,19 +950,11 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr"/>
-      <c r="H8" t="inlineStr"/>
-      <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr"/>
       <c r="N8" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Rawan</t>
@@ -1025,7 +970,6 @@
           <t>Jawa Tengah</t>
         </is>
       </c>
-      <c r="S8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1054,31 +998,21 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr"/>
-      <c r="H9" t="inlineStr"/>
-      <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr"/>
       <c r="N9" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
         <is>
           <t>Jawa Tengah</t>
         </is>
       </c>
-      <c r="S9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1107,19 +1041,11 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr"/>
-      <c r="H10" t="inlineStr"/>
-      <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr"/>
       <c r="N10" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Rawan</t>
@@ -1135,7 +1061,6 @@
           <t>Jawa Tengah</t>
         </is>
       </c>
-      <c r="S10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1164,31 +1089,21 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr"/>
-      <c r="H11" t="inlineStr"/>
-      <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr"/>
       <c r="N11" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
         <is>
           <t>Jawa Tengah</t>
         </is>
       </c>
-      <c r="S11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1217,19 +1132,11 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G12" t="inlineStr"/>
-      <c r="H12" t="inlineStr"/>
-      <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr"/>
       <c r="N12" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Rawan</t>
@@ -1245,7 +1152,6 @@
           <t>Jawa Tengah</t>
         </is>
       </c>
-      <c r="S12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1274,19 +1180,11 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G13" t="inlineStr"/>
-      <c r="H13" t="inlineStr"/>
-      <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr"/>
       <c r="N13" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Rawan</t>
@@ -1302,7 +1200,6 @@
           <t>Jawa Tengah</t>
         </is>
       </c>
-      <c r="S13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1331,17 +1228,11 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G14" t="inlineStr"/>
-      <c r="H14" t="inlineStr"/>
-      <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
-      <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr">
         <is>
           <t>batas ke Subsistem Boyolali 1,2</t>
         </is>
       </c>
-      <c r="M14" t="inlineStr"/>
       <c r="N14" t="inlineStr">
         <is>
           <t>Beroperasi</t>
@@ -1357,13 +1248,11 @@
           <t>Normal</t>
         </is>
       </c>
-      <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr">
         <is>
           <t>Jawa Tengah</t>
         </is>
       </c>
-      <c r="S14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -1392,17 +1281,11 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G15" t="inlineStr"/>
-      <c r="H15" t="inlineStr"/>
-      <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
-      <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr">
         <is>
           <t>batas ke Subsistem Boyolali 1,2</t>
         </is>
       </c>
-      <c r="M15" t="inlineStr"/>
       <c r="N15" t="inlineStr">
         <is>
           <t>Beroperasi</t>
@@ -1418,13 +1301,11 @@
           <t>Normal</t>
         </is>
       </c>
-      <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr">
         <is>
           <t>Jawa Tengah</t>
         </is>
       </c>
-      <c r="S15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -1453,17 +1334,11 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G16" t="inlineStr"/>
-      <c r="H16" t="inlineStr"/>
-      <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
-      <c r="K16" t="inlineStr"/>
       <c r="L16" t="inlineStr">
         <is>
           <t>batas ke Subsistem Kesugihan 1,2</t>
         </is>
       </c>
-      <c r="M16" t="inlineStr"/>
       <c r="N16" t="inlineStr">
         <is>
           <t>Beroperasi</t>
@@ -1479,13 +1354,11 @@
           <t>Normal</t>
         </is>
       </c>
-      <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr">
         <is>
           <t>Jawa Tengah</t>
         </is>
       </c>
-      <c r="S16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -1514,17 +1387,11 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G17" t="inlineStr"/>
-      <c r="H17" t="inlineStr"/>
-      <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
-      <c r="K17" t="inlineStr"/>
       <c r="L17" t="inlineStr">
         <is>
           <t>batas ke Subsistem Pedan 3,4</t>
         </is>
       </c>
-      <c r="M17" t="inlineStr"/>
       <c r="N17" t="inlineStr">
         <is>
           <t>Beroperasi</t>
@@ -1540,13 +1407,11 @@
           <t>Normal</t>
         </is>
       </c>
-      <c r="Q17" t="inlineStr"/>
       <c r="R17" t="inlineStr">
         <is>
           <t>Jawa Tengah</t>
         </is>
       </c>
-      <c r="S17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -1575,17 +1440,11 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G18" t="inlineStr"/>
-      <c r="H18" t="inlineStr"/>
-      <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
-      <c r="K18" t="inlineStr"/>
       <c r="L18" t="inlineStr">
         <is>
           <t>batas ke Subsistem Pedan 3,4</t>
         </is>
       </c>
-      <c r="M18" t="inlineStr"/>
       <c r="N18" t="inlineStr">
         <is>
           <t>Beroperasi</t>
@@ -1601,13 +1460,11 @@
           <t>Normal</t>
         </is>
       </c>
-      <c r="Q18" t="inlineStr"/>
       <c r="R18" t="inlineStr">
         <is>
           <t>Jawa Tengah</t>
         </is>
       </c>
-      <c r="S18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -1636,17 +1493,11 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G19" t="inlineStr"/>
-      <c r="H19" t="inlineStr"/>
-      <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr"/>
-      <c r="K19" t="inlineStr"/>
       <c r="L19" t="inlineStr">
         <is>
           <t>batas ke Subsistem Pedan 3,4</t>
         </is>
       </c>
-      <c r="M19" t="inlineStr"/>
       <c r="N19" t="inlineStr">
         <is>
           <t>Beroperasi</t>
@@ -1662,13 +1513,11 @@
           <t>Normal</t>
         </is>
       </c>
-      <c r="Q19" t="inlineStr"/>
       <c r="R19" t="inlineStr">
         <is>
           <t>Jawa Tengah</t>
         </is>
       </c>
-      <c r="S19" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1800,7 +1649,6 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr"/>
       <c r="H2" t="n">
         <v>2</v>
       </c>
@@ -1814,8 +1662,6 @@
           <t>Sangat Rawan</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr">
         <is>
           <t>Jawa Tengah</t>
@@ -1832,13 +1678,11 @@
           <t>Tidak</t>
         </is>
       </c>
-      <c r="Q2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
         <v>2</v>
       </c>
-      <c r="B3" t="inlineStr"/>
       <c r="C3" t="inlineStr">
         <is>
           <t>SUTT Klaten - Ampel (arah SS Boyolali)</t>
@@ -1859,7 +1703,6 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr"/>
       <c r="H3" t="n">
         <v>2</v>
       </c>
@@ -1873,8 +1716,6 @@
           <t>Normal</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
           <t>Jawa Tengah</t>
@@ -1891,7 +1732,6 @@
           <t>Tidak</t>
         </is>
       </c>
-      <c r="Q3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1922,7 +1762,6 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr"/>
       <c r="H4" t="n">
         <v>2</v>
       </c>
@@ -1936,8 +1775,6 @@
           <t>Sangat Rawan</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
           <t>Jawa Tengah</t>
@@ -1954,7 +1791,6 @@
           <t>Tidak</t>
         </is>
       </c>
-      <c r="Q4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1985,7 +1821,6 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr"/>
       <c r="H5" t="n">
         <v>2</v>
       </c>
@@ -1999,8 +1834,6 @@
           <t>Sangat Rawan</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
           <t>Jawa Tengah</t>
@@ -2017,13 +1850,11 @@
           <t>Tidak</t>
         </is>
       </c>
-      <c r="Q5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
         <v>5</v>
       </c>
-      <c r="B6" t="inlineStr"/>
       <c r="C6" t="inlineStr">
         <is>
           <t>SUTT Bantul - Semanu</t>
@@ -2044,7 +1875,6 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr"/>
       <c r="H6" t="n">
         <v>2</v>
       </c>
@@ -2058,8 +1888,6 @@
           <t>Normal</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
           <t>Jawa Tengah</t>
@@ -2076,7 +1904,6 @@
           <t>Tidak</t>
         </is>
       </c>
-      <c r="Q6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -2107,7 +1934,6 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr"/>
       <c r="H7" t="n">
         <v>2</v>
       </c>
@@ -2121,8 +1947,6 @@
           <t>Sangat Rawan</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
           <t>Jawa Tengah</t>
@@ -2139,13 +1963,11 @@
           <t>Tidak</t>
         </is>
       </c>
-      <c r="Q7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
         <v>7</v>
       </c>
-      <c r="B8" t="inlineStr"/>
       <c r="C8" t="inlineStr">
         <is>
           <t>SUTT Bantul - Wonosari/Gedean (arah SS Pedan 3,4)</t>
@@ -2166,7 +1988,6 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr"/>
       <c r="H8" t="n">
         <v>2</v>
       </c>
@@ -2180,8 +2001,6 @@
           <t>Normal</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
           <t>Jawa Tengah</t>
@@ -2198,7 +2017,6 @@
           <t>Tidak</t>
         </is>
       </c>
-      <c r="Q8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -2229,7 +2047,6 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr"/>
       <c r="H9" t="n">
         <v>2</v>
       </c>
@@ -2243,8 +2060,6 @@
           <t>Sangat Rawan</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
       <c r="M9" t="inlineStr">
         <is>
           <t>Jawa Tengah</t>
@@ -2261,13 +2076,11 @@
           <t>Tidak</t>
         </is>
       </c>
-      <c r="Q9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
         <v>9</v>
       </c>
-      <c r="B10" t="inlineStr"/>
       <c r="C10" t="inlineStr">
         <is>
           <t>SUTT Jajar - Bendono (arah SS Boyolali)</t>
@@ -2288,7 +2101,6 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr"/>
       <c r="H10" t="n">
         <v>2</v>
       </c>
@@ -2302,8 +2114,6 @@
           <t>Normal</t>
         </is>
       </c>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
       <c r="M10" t="inlineStr">
         <is>
           <t>Jawa Tengah</t>
@@ -2320,13 +2130,11 @@
           <t>Tidak</t>
         </is>
       </c>
-      <c r="Q10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
         <v>10</v>
       </c>
-      <c r="B11" t="inlineStr"/>
       <c r="C11" t="inlineStr">
         <is>
           <t>SKTT Jajar - Mangkunegaran</t>
@@ -2347,7 +2155,6 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr"/>
       <c r="H11" t="n">
         <v>2</v>
       </c>
@@ -2361,8 +2168,6 @@
           <t>Normal</t>
         </is>
       </c>
-      <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
       <c r="M11" t="inlineStr">
         <is>
           <t>Jawa Tengah</t>
@@ -2379,7 +2184,6 @@
           <t>Tidak</t>
         </is>
       </c>
-      <c r="Q11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -2410,7 +2214,6 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G12" t="inlineStr"/>
       <c r="H12" t="n">
         <v>2</v>
       </c>
@@ -2424,8 +2227,6 @@
           <t>Sangat Rawan</t>
         </is>
       </c>
-      <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
       <c r="M12" t="inlineStr">
         <is>
           <t>Jawa Tengah</t>
@@ -2442,7 +2243,6 @@
           <t>Tidak</t>
         </is>
       </c>
-      <c r="Q12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -2473,7 +2273,6 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G13" t="inlineStr"/>
       <c r="H13" t="n">
         <v>2</v>
       </c>
@@ -2487,8 +2286,6 @@
           <t>Sangat Rawan</t>
         </is>
       </c>
-      <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
       <c r="M13" t="inlineStr">
         <is>
           <t>Jawa Tengah</t>
@@ -2505,7 +2302,6 @@
           <t>Tidak</t>
         </is>
       </c>
-      <c r="Q13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2536,7 +2332,6 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G14" t="inlineStr"/>
       <c r="H14" t="n">
         <v>2</v>
       </c>
@@ -2550,8 +2345,6 @@
           <t>Sangat Rawan</t>
         </is>
       </c>
-      <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
       <c r="M14" t="inlineStr">
         <is>
           <t>Jawa Tengah</t>
@@ -2568,13 +2361,11 @@
           <t>Tidak</t>
         </is>
       </c>
-      <c r="Q14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
         <v>14</v>
       </c>
-      <c r="B15" t="inlineStr"/>
       <c r="C15" t="inlineStr">
         <is>
           <t>SUTT Palur - Masaran (arah SS Pedan 3,4)</t>
@@ -2595,7 +2386,6 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G15" t="inlineStr"/>
       <c r="H15" t="n">
         <v>2</v>
       </c>
@@ -2609,8 +2399,6 @@
           <t>Normal</t>
         </is>
       </c>
-      <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
       <c r="M15" t="inlineStr">
         <is>
           <t>Jawa Tengah</t>
@@ -2627,7 +2415,6 @@
           <t>Tidak</t>
         </is>
       </c>
-      <c r="Q15" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2696,22 +2483,22 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>[N-1] Pembebanan IBT 1, 2 GITET Pedan &gt;60% sehingga N-1 tidak terpenuhi</t>
+          <t>[N-1] Pembebanan IBT 1, 2 GITET Pedan &gt; 60% sehingga N-1 tidak terpenuhi</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>1.Terjadi Overload&amp; pemadamansaat gangguan salah satu IBT. 2.Berpotensi padam sebesar 611 MW saat terjadi trip 2 IBT GITET Pedan (N-2). 3.Kesulitan dalam pemeliharaan</t>
+          <t>1. Terjadi Overload &amp; pemadamansaat gangguan salah satu IBT. 2. Berpotensi padam sebesar 611 MW saat terjadi trip 2 IBT GITET Pedan (N-2). 3. Kesulitan dalam pemeliharaan</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>1.Sudah terpasang OLS IBT 1,2 Pedan total target sebesar521 MW.(Realisasi BP Tahun 2025, 14 Oktober 2025-5721 MW). 2.Memindahkan GI Banyudono ke SubsistemBoyolali. 3.Splitting di GI 150 kV Sragen sehingga sebagian beban GI Sragen dipasok oleh Subsistem Kediri (UP2B Jawa Timur). 4.Pengaturan pemeliharaan saat beban rendah/hari libur dengan looping 3 IBT Pedan serta pengaturan konfigurasi</t>
+          <t>1.Sudah terpasang OLS IBT 1,2 Pedan total target sebesar 521 MW. (Realisasi BP Tahun 2025, 14 Oktober 2025 -5721 MW). 2.Memindahkan GI Banyudono ke Subsistem Boyolali. 3.Splitting di GI 150 kV Sragen sehingga sebagian beban GI Sragen dipasok oleh Subsistem Kediri (UP2B Jawa Timur). 4.Pengaturan pemeliharaan saat beban rendah/hari libur dengan looping 3 IBT Pedan serta pengaturan konfigurasi</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Jangka Pendek: 1. Rekonduktoring SUTT 150 kV Jajar-Banyudono menjadi HTLSC, 1250 A per sirkit (RUPTL 2025-2034, COD 2026). Update: COD M2 Okt 2026. 2. Pembangunan IBT 3,4 GITET Boyolali (RUPTL 2025-2034 COD 2026 ). 3. Usulan Pembangunan SUTT 150 kV Boyolali-Masaran / SUTT 150 kV Boyolali Gondangrejo. Usulan COD 2027. 4. Rekonduktoring SUTT 150 kV Kedungombo- Purwodadi menjadi HTLSC, 1250 A per sirkit (RUPTL 2025-2034, COD 2026). 5. Pembangunan SUTT 150 kV Sragen-Kedungombo (RUPTL 2025-2034, COD 2026). Update: COD mundur ke 2028</t>
+          <t>Jangka Pendek : 1. Rekonduktoring SUTT 150 kV Jajar-Banyudono menjadi HTLSC, 1250 A per sirkit (RUPTL 2025-2034, COD 2026). Update: COD M2 Okt 2026. 2. Pembangunan IBT 3,4 GITET Boyolali (RUPTL 2025-2034 COD 2026 ). 3. Usulan Pembangunan SUTT 150 kV Boyolali -Masaran / SUTT 150 kV Boyolali Gondangrejo. Usulan COD 2027. 4. Rekonduktoring SUTT 150 kV Kedungombo- Purwodadi menjadi HTLSC, 1250 A per sirkit (RUPTL 2025-2034, COD 2026). 5. Pembangunan SUTT 150 kV Sragen-Kedungombo (RUPTL 2025-2034, COD 2026). Update: COD mundur ke 2028</t>
         </is>
       </c>
     </row>
@@ -2736,7 +2523,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>1.Terjadi Overload&amp; pemadamansaat gangguan salah satu IBT. 2.Fleksibilitas operasi Bus Section berkurang 3.Kesulitan dalam pemeliharaanbusbar</t>
+          <t>1. Terjadi Overload &amp; pemadamansaat gangguan salah satu IBT. 2. Fleksibilitas operasi Bus Section berkurang 3. Kesulitan dalam pemeliharaan busbar</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -2746,7 +2533,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Jangka Pendek: Pembangunan SUTT Pedan- Solobarusesuai (RUPTL 2025- 2034, COD 2027)</t>
+          <t>Jangka Pendek : Pembangunan SUTT Pedan- Solobaru sesuai (RUPTL 2025- 2034, COD 2027)</t>
         </is>
       </c>
     </row>
@@ -2771,17 +2558,17 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>1.Terjadi Overload saat gangguan 1 sirkit diruas tersebut berakibat padam sebesar 195 MW. 2.Berpotensi padam sebesar 206 MW saat terjadi gangguan 2 sirkit (N-2). 3.Kesulitan dalam pemeliharaan</t>
+          <t>1. Terjadi Overload saat gangguan 1 sirkit diruas tersebut berakibat padam sebesar 195 MW. 2. Berpotensi padam sebesar 206 MW saat terjadi gangguan 2 sirkit (N-2). 3. Kesulitan dalam pemeliharaan</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>1.Sudah terpasang OLS SUTT 150 kV Jajar- Gondangrejo dengan total target sebesar225 MW.(Realisasi BP Tahun 2025, 14 Oktober 2025-5.721 MW). 2.Pengoperasian Splitting Busbar di GI 150 kV Palur. 3.Pekerjaan pemeliharaan dilaksanakan pada hari Minggu saat beban rendah</t>
+          <t>1.Sudah terpasang OLS SUTT 150 kV Jajar- Gondangrejo dengan total target sebesar 225 MW. (Realisasi BP Tahun 2025, 14 Oktober 2025 -5.721 MW). 2.Pengoperasian Splitting Busbar di GI 150 kV Palur. 3.Pekerjaan pemeliharaan dilaksanakan pada hari Minggu saat beban rendah</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>JangkaPendek: 1.RekonduktoringSUTT 150 kVKedungombo- PurwodadimenjadiHTLSC, 1250 A persirkit(RUPTL 2025-2034, COD 2026). 2.Pembangunan SUTT 150 kVSragen- Kedungombo(RUPTL 2025- 2034, COD 2026) Update: COD mundur ke 2028. 3.Percepatan rekonduktoring SUTT 150 kV Jajar- Gondangrejo menjadi HTLSC, 1250 A per sirkit (RUPTL 2025-2034, COD Tahun Usulan / Solusi 2026). Update UIT: Akan terkontrak 2026 COD 2027. 4.Usulan Pembangunan SUTT 150 kV Boyolali - Masaran / SUTT 150 kV Boyolali Gondangrejo. Usulan COD 2027</t>
+          <t>Jangka Pendek: 1.Rekonduktoring SUTT 150 kV Kedungombo- Purwodadi menjadiHTLSC, 1250 A per sirkit(RUPTL 2025-2034, COD 2026). 2.Pembangunan SUTT 150 kV Sragen- Kedungombo (RUPTL 2025- 2034, COD 2026) Update: COD mundur ke 2028. 3.Percepatan rekonduktoring SUTT 150 kV Jajar- Gondangrejo menjadi HTLSC, 1250 A per sirkit (RUPTL 2025-2034, COD Tahun Usulan / Solusi 2026). Update UIT: Akan terkontrak 2026 COD 2027. 4.Usulan Pembangunan SUTT 150 kV Boyolali - Masaran / SUTT 150 kV Boyolali Gondangrejo. Usulan COD 2027</t>
         </is>
       </c>
     </row>
@@ -2806,17 +2593,17 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>1.Terjadi Overload saat gangguan 1 sirkit diruas tersebut berakibat padam sebesar 195 MW. 2.Berpotensi padam sebesar 130 MW saat terjadi gangguan 2 sirkit (N-2). 3.Kesulitan dalam pemeliharaan</t>
+          <t>1. Terjadi Overload saat gangguan 1 sirkit diruas tersebut berakibat padam sebesar 195 MW. 2. Berpotensi padam sebesar 130 MW saat terjadi gangguan 2 sirkit (N-2). 3. Kesulitan dalam pemeliharaan</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>1. Sudah terpasang OLS SUTT 150 kV Gondangrejo-Palur dengan total target sebesar179 MW.(Realisasi BP Tahun 2025, 14 Oktober 2025-5721 MW). 2. Pengoperasian Splitting Busbar di GI 150 kV Palur. 3. Pekerjaan pemeliharaan dilaksanakan pada hari Minggu saat beban rendah</t>
+          <t>1. Sudah terpasang OLS SUTT 150 kV Gondangrejo-Palur dengan total target sebesar 179 MW. (Realisasi BP Tahun 2025, 14 Oktober 2025 -5721 MW). 2. Pengoperasian Splitting Busbar di GI 150 kV Palur. 3. Pekerjaan pemeliharaan dilaksanakan pada hari Minggu saat beban rendah</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>JangkaPendek: 1.RekonduktoringSUTT 150 kVKedungombo- PurwodadimenjadiHTLSC, 1250 A persirkit(RUPTL 2025-2034, COD 2026). 2.Pembangunan SUTT 150 kVSragen- Kedungombo(RUPTL 2025- 2034, COD 2026). Update: COD mundur ke 2028. 3.Percepatan rekonduktoring SUTT 150 kV Gondangrejo- Palur menjadi HTLSC, 1250 A per sirkit (RUPTL 2025-2034, COD Tahun 2027). Update UIT: Akan terkontrak 2026 COD 2027. 4.Usulan Pembangunan SUTT 150 kV Boyolali - Masaran / SUTT 150 kV Boyolali Gondangrejo. Usulan COD 2027</t>
+          <t>Jangka Pendek: 1.Rekonduktoring SUTT 150 kV Kedungombo- Purwodadi menjadiHTLSC, 1250 A per sirkit(RUPTL 2025-2034, COD 2026). 2.Pembangunan SUTT 150 kV Sragen- Kedungombo (RUPTL 2025- 2034, COD 2026). Update: COD mundur ke 2028. 3.Percepatan rekonduktoring SUTT 150 kV Gondangrejo- Palur menjadi HTLSC, 1250 A per sirkit (RUPTL 2025-2034, COD Tahun 2027). Update UIT: Akan terkontrak 2026 COD 2027. 4.Usulan Pembangunan SUTT 150 kV Boyolali - Masaran / SUTT 150 kV Boyolali Gondangrejo. Usulan COD 2027</t>
         </is>
       </c>
     </row>
@@ -2841,7 +2628,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>1.Terjadi Overload saat gangguan 1 sirkit diruas tersebut. 2.Berpotensi padam sebesar 196 MW jika terjadi trip 2 penghantar ruas SUTT 150 kV Bantul-Klaten (N-2). 3.Kesulitan dalam pemeliharaan</t>
+          <t>1. Terjadi Overload saat gangguan 1 sirkit diruas tersebut. 2. Berpotensi padam sebesar 196 MW jika terjadi trip 2 penghantar ruas SUTT 150 kV Bantul-Klaten (N-2). 3. Kesulitan dalam pemeliharaan</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -2851,7 +2638,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Jangka Pendek: 1.PercepatanpembangunanS UTTPedan-Kalasan (RUPTL 2025-2034, COD 2026). 2.PercepatanpembangunanS UTTKalasan- BantulsesuaiRUPTL 2025- 2034, CODTahun2026). *Update: Point 1,2 sudah disetujui di TVV</t>
+          <t>Jangka Pendek : 1.Percepatanpembangunan S UTT Pedan-Kalasan (RUPTL 2025-2034, COD 2026). 2.Percepatanpembangunan S UTT Kalasan- Bantul sesuaiRUPTL 2025- 2034, COD Tahun2026). *Update: Point 1,2 sudah disetujui di TVV</t>
         </is>
       </c>
     </row>
@@ -2876,7 +2663,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>1.Terjadi Overload saat gangguan 1 sirkit diruas tersebut. 2.Berpotensi padam sebesar 158 MW jika terjadi trip 2 penghantar ruas SUTT 150 kV Bantul-Klaten (N-2). 3.Kesulitan dalam pemeliharaan</t>
+          <t>1. Terjadi Overload saat gangguan 1 sirkit diruas tersebut. 2. Berpotensi padam sebesar 158 MW jika terjadi trip 2 penghantar ruas SUTT 150 kV Bantul-Klaten (N-2). 3. Kesulitan dalam pemeliharaan</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -2886,7 +2673,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Jangka Pendek: 1.PercepatanpembangunanS UTTPedan-Kalasan (RUPTL 2025-2034, COD 2026). 2.PercepatanpembangunanS UTTKalasan- BantulsesuaiRUPTL 2025- 2034, CODTahun2026). *Update: Point 1,2 sudah disetujui di TVV</t>
+          <t>Jangka Pendek : 1.Percepatanpembangunan S UTT Pedan-Kalasan (RUPTL 2025-2034, COD 2026). 2.Percepatanpembangunan S UTT Kalasan- Bantul sesuaiRUPTL 2025- 2034, COD Tahun2026). *Update: Point 1,2 sudah disetujui di TVV</t>
         </is>
       </c>
     </row>
@@ -2911,7 +2698,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>1.Terjadi Drop tegangan di sisi 20 kV bila dilakukan manuver pemindahan beban. apabila terjadi gangguan di trafo GI 150 kV Palur. 2.Pertumbuhan beban di sisi 20 kV GI Palur terhambat</t>
+          <t>1. Terjadi Drop tegangan di sisi 20 kV bila dilakukan manuver pemindahan beban. apabila terjadi gangguan di trafo GI 150 kV Palur. 2. Pertumbuhan beban di sisi 20 kV GI Palur terhambat</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -2941,12 +2728,12 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>[N-1] Pembebanan Trafo di GI 150 kV Bantul&gt;80% sehinggaN- 1tidakterpenuhi</t>
+          <t>[N-1] Pembebanan Trafo di GI 150 kV Bantul &gt;80% sehingga N- 1 tidakterpenuhi</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>1.Terjadi Drop tegangan di sisi 20 kV bila dilakukan manuver pemindahan beban apabila terjadi gangguan di trafo GI 150 kV Bantul. 2.Potensi pertumbuhan beban terhambat di GI Bantul</t>
+          <t>1. Terjadi Drop tegangan di sisi 20 kV bila dilakukan manuver pemindahan beban apabila terjadi gangguan di trafo GI 150 kV Bantul. 2. Potensi pertumbuhan beban terhambat di GI Bantul</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -2956,7 +2743,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Jangka Pendek: 1.Extension Trafo4-60 MVA GI Bantul. Sesuai RUPTL 2025- 2034, COD 2026. Jangka Menegah: 2.Pembangunan GI 150 kV Bantul II (Tuksono). Sesuai RUPTL 2025-2034, COD 2030), diusulkan COD dipercepat2026. Progres: 0%. Prioritas: P3</t>
+          <t>Jangka Pendek: 1.Extension Trafo 4-60 MVA GI Bantul. Sesuai RUPTL 2025- 2034, COD 2026. Jangka Menegah: 2.Pembangunan GI 150 kV Bantul II (Tuksono). Sesuai RUPTL 2025-2034, COD 2030), diusulkan COD dipercepat 2026. Progres: 0%. Prioritas: P3</t>
         </is>
       </c>
     </row>
@@ -2976,22 +2763,22 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>[N-1] PembebananSUTT 150 kV Pedan-Klaten 1,2 &gt;50% sehinggaN- 1tidakterpenuhi. Hal ini diakibatkan adanya penurunan kapasitas penghantar setelah dipindahkanke Tower Emergency pasca tower roboh tahun 2025.(semula@1285 Amenjadi@800 A)</t>
+          <t>[N-1] Pembebanan SUTT 150 kV Pedan-Klaten 1,2 &gt;50% sehingga N- 1 tidakterpenuhi. Hal ini diakibatkan adanya penurunan kapasitas penghantar setelah dipindahkanke Tower Emergency pasca tower roboh tahun 2025. (semula@1285 A menjadi@800 A)</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>1.TerjadiOverloadsaatg angguan1sirkitdiruast ersebut. 2.Berpotensipadamsebe sar216MWjikaterjadi trip 2penghantarruasSUTT 150 kV Pedan - Klaten(N-2). 3.Kesulitandalampemeli haraan</t>
+          <t>1.Terjadi Overloadsaatg angguan1sirkitdiruast ersebut. 2.Berpotensipadamsebe sar216MWjika terjadi trip 2penghantarruas SUTT 150 kV Pedan - Klaten (N-2). 3.Kesulitandalampemeli haraan</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>1.Pembatasanpasokank ewilayah Bantul (Yogyakarta) dan Klaten sesuaidengankemamp uan kapasitas1sirkitpengh antar@800 A persirkit. 2.PengoperasianSplitting Busbardi GI 150 kV Bantul dan GI 150 kV Klaten. 3.Pengaturanpemelihara anpadasaatbebanren dah/harilibur. 4.PemasanganOLS SUTT Pedan- Klaten,aktifApril 2026</t>
+          <t>1.Pembatasanpasokank ewilayah Bantul (Yogyakarta) dan Klaten sesuaidengankemamp uan kapasitas 1sirkitpengh antar@800 A per sirkit. 2.Pengoperasian Splitting Busbar di GI 150 kV Bantul dan GI 150 kV Klaten. 3.Pengaturanpemelihara anpadasaatbebanren dah/hari libur. 4.Pemasangan OLS SUTT Pedan- Klaten,aktif April 2026</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Jangka Pendek: 1.PercepatanpembangunanS UTTPedan- Kalasan(RUPTL 2025-2034, COD 2026). 2.Percepatan pembangunan SUTT kalasan - Bantul seuai RUPTL 2025-2034, CODTahun2026)</t>
+          <t>Jangka Pendek: 1.Percepatanpembangunan S UTT Pedan- Kalasan (RUPTL 2025-2034, COD 2026). 2.Percepatan pembangunan SUTT kalasan - Bantul seuai RUPTL 2025-2034, COD Tahun2026)</t>
         </is>
       </c>
     </row>
@@ -3016,7 +2803,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>1.Terjadi Overload saat gangguan 1 sirkit diruas tersebut. 2.Berpotensi padam sebesar 400 MW jika terjadi trip 2 penghantar ruas SUTT 150 kV Pedan-Jajar (N- 2). 3.Kesulitan dalam pemeliharaan</t>
+          <t>1. Terjadi Overload saat gangguan 1 sirkit diruas tersebut. 2. Berpotensi padam sebesar 400 MW jika terjadi trip 2 penghantar ruas SUTT 150 kV Pedan -Jajar (N- 2). 3. Kesulitan dalam pemeliharaan</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -3026,7 +2813,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Jangka Pendek: 1.Pembangunan SUTT Pedan- SoloBarusesuai (RUPTL 2025-2034, COD Tahun 2027). 2.RekonduktoringSUTT 150 kVKedungombo- PurwodadimenjadiHTLSC, 1250 A persirkit(RUPTL 2025-2034, COD 2026). 3.Pembangunan SUTT 150 kVSragen- Kedungombo(RUPTL 2025- 2034, COD 2026). Update: COD mundur ke 2028</t>
+          <t>Jangka Pendek: 1.Pembangunan SUTT Pedan- SoloBaru sesuai (RUPTL 2025-2034, COD Tahun 2027). 2.Rekonduktoring SUTT 150 kV Kedungombo- Purwodadi menjadiHTLSC, 1250 A per sirkit(RUPTL 2025-2034, COD 2026). 3.Pembangunan SUTT 150 kV Sragen- Kedungombo (RUPTL 2025- 2034, COD 2026). Update: COD mundur ke 2028</t>
         </is>
       </c>
     </row>
